--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_REINA PROTEÍNAS CLAVIJO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_REINA PROTEÍNAS CLAVIJO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>66.7863</v>
+        <v>58.9369</v>
       </c>
       <c r="E2" t="n">
-        <v>51.5748</v>
+        <v>43.189</v>
       </c>
       <c r="F2" t="n">
-        <v>15.2114</v>
+        <v>15.7475</v>
       </c>
       <c r="G2" t="n">
         <v>17.7234</v>
@@ -610,13 +610,13 @@
         <v>48.4914</v>
       </c>
       <c r="S2" t="n">
-        <v>25.2661</v>
+        <v>17.4165</v>
       </c>
       <c r="T2" t="n">
-        <v>17.5441</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>7.7222</v>
+        <v>8.2583</v>
       </c>
       <c r="V2" t="n">
         <v>7.3556</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>36.3678</v>
+        <v>56.6036</v>
       </c>
       <c r="E3" t="n">
-        <v>40.453</v>
+        <v>52.6368</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.085500000000001</v>
+        <v>3.9666</v>
       </c>
       <c r="G3" t="n">
         <v>32.0164</v>
@@ -688,13 +688,13 @@
         <v>38.5017</v>
       </c>
       <c r="S3" t="n">
-        <v>-16.4945</v>
+        <v>3.741</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.355699999999999</v>
+        <v>2.828</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.139</v>
+        <v>0.9133</v>
       </c>
       <c r="V3" t="n">
         <v>25.6325</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>25.9185</v>
+        <v>20.6374</v>
       </c>
       <c r="E4" t="n">
-        <v>19.3082</v>
+        <v>13.1309</v>
       </c>
       <c r="F4" t="n">
-        <v>6.610500000000001</v>
+        <v>7.5067</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1590999999999994</v>
@@ -766,13 +766,13 @@
         <v>37.2533</v>
       </c>
       <c r="S4" t="n">
-        <v>23.7246</v>
+        <v>18.4436</v>
       </c>
       <c r="T4" t="n">
-        <v>19.6236</v>
+        <v>13.4459</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1012</v>
+        <v>4.997400000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-10.5502</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>24.2695</v>
+        <v>10.6779</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0855</v>
+        <v>1.645500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>17.184</v>
+        <v>9.032500000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5925</v>
+        <v>18.6982</v>
       </c>
       <c r="H5" t="n">
-        <v>1.883</v>
+        <v>2.021299999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7093</v>
+        <v>16.6765</v>
       </c>
       <c r="J5" t="n">
-        <v>13.4048</v>
+        <v>28.541</v>
       </c>
       <c r="K5" t="n">
-        <v>9.2508</v>
+        <v>9.8681</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1543</v>
+        <v>18.6726</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.812200000000001</v>
+        <v>-9.8428</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.3679</v>
+        <v>-7.8468</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5555000000000003</v>
+        <v>-1.9958</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0404</v>
+        <v>-2.497399999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-28.9286</v>
+        <v>-38.9184</v>
       </c>
       <c r="R5" t="n">
-        <v>27.8879</v>
+        <v>36.4206</v>
       </c>
       <c r="S5" t="n">
-        <v>42.0439</v>
+        <v>6.7116</v>
       </c>
       <c r="T5" t="n">
-        <v>23.7593</v>
+        <v>2.5054</v>
       </c>
       <c r="U5" t="n">
-        <v>18.2846</v>
+        <v>4.2059</v>
       </c>
       <c r="V5" t="n">
-        <v>-23.3261</v>
+        <v>-12.2344</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.1498</v>
+        <v>9.517299999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-22.1762</v>
+        <v>-21.7514</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>22.8128</v>
+        <v>10.6382</v>
       </c>
       <c r="E6" t="n">
-        <v>16.828</v>
+        <v>2.184699999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9848</v>
+        <v>8.453100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>11.5917</v>
+        <v>-2.7911</v>
       </c>
       <c r="H6" t="n">
-        <v>15.9367</v>
+        <v>8.7865</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.3449</v>
+        <v>-11.5778</v>
       </c>
       <c r="J6" t="n">
-        <v>22.0211</v>
+        <v>3.5145</v>
       </c>
       <c r="K6" t="n">
-        <v>22.7045</v>
+        <v>12.2147</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6833</v>
+        <v>-8.700099999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-10.4294</v>
+        <v>-6.305499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.7679</v>
+        <v>-3.4277</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.6617</v>
+        <v>-2.8779</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2487</v>
+        <v>9.3653</v>
       </c>
       <c r="Q6" t="n">
-        <v>-24.5581</v>
+        <v>-13.5278</v>
       </c>
       <c r="R6" t="n">
-        <v>25.8068</v>
+        <v>22.893</v>
       </c>
       <c r="S6" t="n">
-        <v>26.5549</v>
+        <v>4.4919</v>
       </c>
       <c r="T6" t="n">
-        <v>16.4109</v>
+        <v>2.062</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1443</v>
+        <v>2.4305</v>
       </c>
       <c r="V6" t="n">
-        <v>-16.5824</v>
+        <v>-0.4279999999999997</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9542</v>
+        <v>10.1363</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.5365</v>
+        <v>-10.5642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>12.1083</v>
+        <v>9.1402</v>
       </c>
       <c r="E7" t="n">
-        <v>5.371300000000001</v>
+        <v>7.645300000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>6.736899999999999</v>
+        <v>1.495</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7911</v>
+        <v>11.5917</v>
       </c>
       <c r="H7" t="n">
-        <v>8.7865</v>
+        <v>15.9367</v>
       </c>
       <c r="I7" t="n">
-        <v>-11.5778</v>
+        <v>-4.3449</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5145</v>
+        <v>22.0211</v>
       </c>
       <c r="K7" t="n">
-        <v>12.2147</v>
+        <v>22.7045</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.700099999999999</v>
+        <v>-0.6833</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.305499999999999</v>
+        <v>-10.4294</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.4277</v>
+        <v>-6.7679</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.8779</v>
+        <v>-3.6617</v>
       </c>
       <c r="P7" t="n">
-        <v>9.3653</v>
+        <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-13.5278</v>
+        <v>-24.5581</v>
       </c>
       <c r="R7" t="n">
-        <v>22.893</v>
+        <v>25.8068</v>
       </c>
       <c r="S7" t="n">
-        <v>5.9623</v>
+        <v>12.8824</v>
       </c>
       <c r="T7" t="n">
-        <v>5.2483</v>
+        <v>7.2283</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7136000000000001</v>
+        <v>5.654199999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4279999999999997</v>
+        <v>-16.5824</v>
       </c>
       <c r="W7" t="n">
-        <v>10.1363</v>
+        <v>2.9542</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.5642</v>
+        <v>-19.5365</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>8.9916</v>
+        <v>5.2809</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1717</v>
+        <v>-4.4887</v>
       </c>
       <c r="F8" t="n">
-        <v>10.1634</v>
+        <v>9.77</v>
       </c>
       <c r="G8" t="n">
         <v>0.7086</v>
@@ -1078,13 +1078,13 @@
         <v>15.6089</v>
       </c>
       <c r="S8" t="n">
-        <v>9.015499999999999</v>
+        <v>5.3051</v>
       </c>
       <c r="T8" t="n">
-        <v>8.448600000000001</v>
+        <v>5.131600000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5669000000000001</v>
+        <v>0.1735</v>
       </c>
       <c r="V8" t="n">
         <v>-1.9813</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. PA MOR</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>3.816</v>
+        <v>3.430400000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4447</v>
+        <v>-5.912299999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3712</v>
+        <v>9.3431</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6173999999999995</v>
+        <v>6.5925</v>
       </c>
       <c r="H9" t="n">
-        <v>6.3331</v>
+        <v>1.883</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.715800000000001</v>
+        <v>4.7093</v>
       </c>
       <c r="J9" t="n">
-        <v>4.754</v>
+        <v>13.4048</v>
       </c>
       <c r="K9" t="n">
-        <v>8.000299999999999</v>
+        <v>9.2508</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.246</v>
+        <v>4.1543</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1365</v>
+        <v>-6.812200000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6669</v>
+        <v>-7.3679</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4695</v>
+        <v>0.5555000000000003</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.619199999999999</v>
+        <v>-1.0404</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.6495</v>
+        <v>-28.9286</v>
       </c>
       <c r="R9" t="n">
-        <v>11.0303</v>
+        <v>27.8879</v>
       </c>
       <c r="S9" t="n">
-        <v>8.562799999999999</v>
+        <v>21.2046</v>
       </c>
       <c r="T9" t="n">
-        <v>6.6886</v>
+        <v>10.7612</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8743</v>
+        <v>10.4433</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2547000000000001</v>
+        <v>-23.3261</v>
       </c>
       <c r="W9" t="n">
-        <v>6.651400000000001</v>
+        <v>-1.1498</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.3966</v>
+        <v>-22.1762</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.395200000000001</v>
+        <v>2.4923</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2079</v>
+        <v>-3.654999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6032</v>
+        <v>6.1474</v>
       </c>
       <c r="G10" t="n">
         <v>1.3162</v>
@@ -1234,13 +1234,13 @@
         <v>8.741</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5146999999999999</v>
+        <v>0.5821</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2066</v>
+        <v>0.7593</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7215</v>
+        <v>-0.1771</v>
       </c>
       <c r="V10" t="n">
         <v>1.6344</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PASCUAL BLANCO</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4909</v>
+        <v>1.037300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6216999999999999</v>
+        <v>-13.1274</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1305000000000001</v>
+        <v>14.1646</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6127</v>
+        <v>-15.2217</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5735</v>
+        <v>-6.863</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03919999999999998</v>
+        <v>-8.358499999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5720000000000001</v>
+        <v>-8.674200000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2472</v>
+        <v>1.1989</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6752</v>
+        <v>-9.873099999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04069999999999999</v>
+        <v>-6.547499999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6736</v>
+        <v>-8.062200000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7144</v>
+        <v>1.5146</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6243000000000001</v>
+        <v>11.8627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2081</v>
+        <v>-15.4008</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8324</v>
+        <v>27.2632</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4215</v>
+        <v>2.8714</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2577</v>
+        <v>2.1203</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1638</v>
+        <v>0.7511</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1675</v>
+        <v>1.5248</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>8.827400000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-7.3023</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MIRANDA PASCUAL</t>
+          <t>R. PASCUAL BLANCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3553</v>
+        <v>0.1402999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6199</v>
+        <v>0.3001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2646</v>
+        <v>-0.1599</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1474</v>
+        <v>0.6127</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8613999999999999</v>
+        <v>0.5735</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.286</v>
+        <v>0.03919999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.1881</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3306000000000001</v>
+        <v>1.2472</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.8575</v>
+        <v>-0.6752</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04059999999999997</v>
+        <v>0.04069999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5307999999999999</v>
+        <v>-0.6736</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5715</v>
+        <v>0.7144</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8324</v>
+        <v>0.6243000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.2081</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0406</v>
+        <v>0.8324</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9597</v>
+        <v>0.07059999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7763</v>
+        <v>-0.06380000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1834</v>
+        <v>0.1343</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>D. PA MOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.971000000000001</v>
+        <v>-1.0784</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.8517</v>
+        <v>-2.1752</v>
       </c>
       <c r="F13" t="n">
-        <v>11.8809</v>
+        <v>1.0971</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.2217</v>
+        <v>0.6173999999999995</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.863</v>
+        <v>6.3331</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.358499999999999</v>
+        <v>-5.715800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.674200000000001</v>
+        <v>4.754</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1989</v>
+        <v>8.000299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.873099999999999</v>
+        <v>-3.246</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.547499999999999</v>
+        <v>-4.1365</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.062200000000001</v>
+        <v>-1.6669</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5146</v>
+        <v>-2.4695</v>
       </c>
       <c r="P13" t="n">
-        <v>11.8627</v>
+        <v>-5.619199999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.4008</v>
+        <v>-16.6495</v>
       </c>
       <c r="R13" t="n">
-        <v>27.2632</v>
+        <v>11.0303</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.1369</v>
+        <v>3.6688</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.604</v>
+        <v>3.0688</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5331</v>
+        <v>0.6001000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5248</v>
+        <v>0.2547000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.827400000000001</v>
+        <v>6.651400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.3023</v>
+        <v>-6.3966</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>D. MIRANDA PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.092000000000001</v>
+        <v>-1.8258</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.805</v>
+        <v>-3.0904</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7129</v>
+        <v>1.2647</v>
       </c>
       <c r="G14" t="n">
-        <v>18.6982</v>
+        <v>-3.1474</v>
       </c>
       <c r="H14" t="n">
-        <v>2.021299999999999</v>
+        <v>-0.8613999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>16.6765</v>
+        <v>-2.286</v>
       </c>
       <c r="J14" t="n">
-        <v>28.541</v>
+        <v>-3.1881</v>
       </c>
       <c r="K14" t="n">
-        <v>9.8681</v>
+        <v>-0.3306000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>18.6726</v>
+        <v>-2.8575</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.8428</v>
+        <v>0.04059999999999997</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.8468</v>
+        <v>-0.5307999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9958</v>
+        <v>0.5715</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.497399999999999</v>
+        <v>0.8324</v>
       </c>
       <c r="Q14" t="n">
-        <v>-38.9184</v>
+        <v>-0.2081</v>
       </c>
       <c r="R14" t="n">
-        <v>36.4206</v>
+        <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.0588</v>
+        <v>0.4891</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.9451</v>
+        <v>0.3058</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8862999999999999</v>
+        <v>0.1833</v>
       </c>
       <c r="V14" t="n">
-        <v>-12.2344</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>9.517299999999999</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-21.7514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-43.3194</v>
+        <v>-22.175</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.3756</v>
+        <v>-11.5555</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.944</v>
+        <v>-10.6199</v>
       </c>
       <c r="G15" t="n">
         <v>7.4301</v>
@@ -1624,13 +1624,13 @@
         <v>37.6695</v>
       </c>
       <c r="S15" t="n">
-        <v>-20.1685</v>
+        <v>0.9758999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-13.4707</v>
+        <v>1.3496</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.6976</v>
+        <v>-0.3739000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-19.5505</v>
@@ -1657,13 +1657,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>-52.0024</v>
+        <v>-36.6238</v>
       </c>
       <c r="E16" t="n">
-        <v>-57.0239</v>
+        <v>-45.2879</v>
       </c>
       <c r="F16" t="n">
-        <v>5.0216</v>
+        <v>8.664099999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-9.3904</v>
@@ -1702,13 +1702,13 @@
         <v>31.0097</v>
       </c>
       <c r="S16" t="n">
-        <v>-12.8664</v>
+        <v>2.5125</v>
       </c>
       <c r="T16" t="n">
-        <v>-11.3605</v>
+        <v>0.3755999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5055</v>
+        <v>2.1372</v>
       </c>
       <c r="V16" t="n">
         <v>-3.3152</v>
@@ -1735,22 +1735,22 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>94.21680000000001</v>
+        <v>117.3124</v>
       </c>
       <c r="E17" t="n">
-        <v>22.63150000000002</v>
+        <v>31.43990000000002</v>
       </c>
       <c r="F17" t="n">
-        <v>71.58540000000001</v>
+        <v>85.87260000000003</v>
       </c>
       <c r="G17" t="n">
-        <v>66.5975</v>
+        <v>66.59750000000001</v>
       </c>
       <c r="H17" t="n">
         <v>45.16689999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>21.4296</v>
+        <v>21.42959999999999</v>
       </c>
       <c r="J17" t="n">
         <v>200.5629</v>
@@ -1759,7 +1759,7 @@
         <v>144.0497</v>
       </c>
       <c r="L17" t="n">
-        <v>56.5146</v>
+        <v>56.51459999999999</v>
       </c>
       <c r="M17" t="n">
         <v>-133.9649</v>
@@ -1768,10 +1768,10 @@
         <v>-98.88160000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-35.08379999999999</v>
+        <v>-35.0838</v>
       </c>
       <c r="P17" t="n">
-        <v>2.081799999999998</v>
+        <v>2.081799999999991</v>
       </c>
       <c r="Q17" t="n">
         <v>-368.3712</v>
@@ -1780,13 +1780,13 @@
         <v>370.4503</v>
       </c>
       <c r="S17" t="n">
-        <v>78.2715</v>
+        <v>101.3671</v>
       </c>
       <c r="T17" t="n">
-        <v>52.22800000000002</v>
+        <v>61.03600000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>26.0439</v>
+        <v>40.33140000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-52.7336</v>
